--- a/public/Отчёт_10.02.2026_ночь.xlsx
+++ b/public/Отчёт_10.02.2026_ночь.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Наряд за</t>
   </si>
@@ -44,7 +44,10 @@
     <t>Тоннаж (чел-часы)</t>
   </si>
   <si>
-    <t>Первая фис машина (23 отсадки, зефир с начинкой - 19 отсадок)</t>
+    <t>Первая фис машина</t>
+  </si>
+  <si>
+    <t>ТОННАЖ ПЛАН</t>
   </si>
   <si>
     <t>Муминова Садокат Муроджоновна</t>
@@ -53,12 +56,18 @@
     <t>Андреева Алина Николаевна</t>
   </si>
   <si>
+    <t>ТОННАЖ ФАКТ</t>
+  </si>
+  <si>
     <t>Атахонова Хаётхон Гуломжоновна</t>
   </si>
   <si>
     <t>Бекчанова Манзура Алимбаевна</t>
   </si>
   <si>
+    <t>ОТКЛОНЕНИЕ</t>
+  </si>
+  <si>
     <t>ИТОГО</t>
   </si>
   <si>
@@ -99,6 +108,21 @@
   </si>
   <si>
     <t>ИП Роганов</t>
+  </si>
+  <si>
+    <t>Заместитель генерального директора</t>
+  </si>
+  <si>
+    <t>Корнилова Л.А.</t>
+  </si>
+  <si>
+    <t>Начальник производства</t>
+  </si>
+  <si>
+    <t>Начальник смены</t>
+  </si>
+  <si>
+    <t>Мастер варки</t>
   </si>
 </sst>
 </file>
@@ -179,16 +203,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I33"/>
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -255,14 +279,16 @@
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4"/>
-      <c r="H4"/>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
       <c r="I4">
-        <v>1.7391304347826</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4">
         <v>21.27</v>
@@ -284,10 +310,13 @@
         <f>=E5 * F5</f>
         <v>formula</v>
       </c>
+      <c r="H5">
+        <v>1995</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4">
         <v>4.40</v>
@@ -309,10 +338,13 @@
         <f>=E6 * F6</f>
         <v>formula</v>
       </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4">
         <v>4.40</v>
@@ -337,7 +369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4">
         <v>4.40</v>
@@ -359,10 +391,13 @@
         <f>=E8 * F8</f>
         <v>formula</v>
       </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4">
         <v>2.90</v>
@@ -384,10 +419,14 @@
         <f>=E9 * F9</f>
         <v>formula</v>
       </c>
+      <c r="H9" t="str">
+        <f>=H5-H7</f>
+        <v>formula</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" t="str" s="5">
         <f>=SUM(B5:B9)</f>
@@ -413,7 +452,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
@@ -426,7 +465,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" s="4">
         <v>0.42</v>
@@ -451,7 +490,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4">
         <v>0.15</v>
@@ -476,7 +515,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B14" t="str" s="5">
         <f>=SUM(B12:B13)</f>
@@ -502,7 +541,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -512,12 +551,12 @@
       <c r="G15"/>
       <c r="H15"/>
       <c r="I15">
-        <v>0.68426197458456</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B16" s="4">
         <v>0.62</v>
@@ -542,7 +581,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4">
         <v>0.05</v>
@@ -567,7 +606,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4">
         <v>0.07</v>
@@ -592,7 +631,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B19" t="str" s="5">
         <f>=SUM(B16:B18)</f>
@@ -621,7 +660,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B21" t="str">
         <f>=B4 + B11 + B15</f>
@@ -650,7 +689,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B22" t="str">
         <f>=B10 + B14 + B19</f>
@@ -680,7 +719,7 @@
     <row r="23"/>
     <row r="24">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -701,12 +740,12 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B25" t="str">
         <f>=(B5+B6+B7+B8+B9+B12+B13+B16+B17+B18)</f>
@@ -736,7 +775,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B26"/>
       <c r="C26"/>
@@ -748,7 +787,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
@@ -760,7 +799,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
@@ -772,7 +811,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
@@ -782,6 +821,34 @@
       <c r="G29"/>
       <c r="H29"/>
     </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/public/Отчёт_10.02.2026_ночь.xlsx
+++ b/public/Отчёт_10.02.2026_ночь.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Наряд за</t>
   </si>
@@ -41,9 +41,6 @@
     <t>Примечание</t>
   </si>
   <si>
-    <t>Тоннаж (чел-часы)</t>
-  </si>
-  <si>
     <t>Первая фис машина</t>
   </si>
   <si>
@@ -53,34 +50,40 @@
     <t>Муминова Садокат Муроджоновна</t>
   </si>
   <si>
+    <t>Алимов Ислом Шодмон угли</t>
+  </si>
+  <si>
+    <t>ТОННАЖ ФАКТ</t>
+  </si>
+  <si>
     <t>Андреева Алина Николаевна</t>
   </si>
   <si>
-    <t>ТОННАЖ ФАКТ</t>
-  </si>
-  <si>
     <t>Атахонова Хаётхон Гуломжоновна</t>
   </si>
   <si>
+    <t>ОТКЛОНЕНИЕ</t>
+  </si>
+  <si>
+    <t>ИТОГО</t>
+  </si>
+  <si>
+    <t>FLOY PAK 7 с апликатором</t>
+  </si>
+  <si>
+    <t>Демьянов Станислав Владимирович</t>
+  </si>
+  <si>
+    <t>НЕПРЕРЫВНАЯ ЛИНИЯ №2 - Шоколадная линия 2</t>
+  </si>
+  <si>
+    <t>Мухсинжонова</t>
+  </si>
+  <si>
     <t>Бекчанова Манзура Алимбаевна</t>
   </si>
   <si>
-    <t>ОТКЛОНЕНИЕ</t>
-  </si>
-  <si>
-    <t>ИТОГО</t>
-  </si>
-  <si>
-    <t>FLOY PAK 7 с апликатором</t>
-  </si>
-  <si>
-    <t>Демьянов Станислав Владимирович</t>
-  </si>
-  <si>
-    <t>НЕПРЕРЫВНАЯ ЛИНИЯ №2 - Шоколадная линия 2</t>
-  </si>
-  <si>
-    <t>Мухсинжонова</t>
+    <t>Алимардонова Саидахон</t>
   </si>
   <si>
     <t>ИТОГО ПО ЗАДАНИЮ</t>
@@ -92,7 +95,13 @@
     <t>КОМПАНИИ</t>
   </si>
   <si>
-    <t>Тоннаж</t>
+    <t>Тоннаж (зефир)</t>
+  </si>
+  <si>
+    <t>Тоннаж (конфеты)</t>
+  </si>
+  <si>
+    <t>Тоннаж (суфле)</t>
   </si>
   <si>
     <t>Сокол</t>
@@ -203,7 +212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:J36"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -212,8 +221,9 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -265,13 +275,10 @@
       <c r="H3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -280,15 +287,12 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4">
-        <v>540</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4">
         <v>21.27</v>
@@ -311,15 +315,15 @@
         <v>formula</v>
       </c>
       <c r="H5">
-        <v>1995</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="4">
-        <v>4.40</v>
+        <v>16.08</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -339,15 +343,15 @@
         <v>formula</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="4">
-        <v>4.40</v>
+        <v>16.08</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -369,10 +373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="4">
-        <v>4.40</v>
+        <v>16.08</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -392,31 +396,32 @@
         <v>formula</v>
       </c>
       <c r="H8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="5">
         <v>18</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2.90</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.00</v>
-      </c>
-      <c r="E9" t="str">
-        <f>=C9 - D9</f>
-        <v>formula</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="str">
-        <f>=E9 * F9</f>
+      <c r="B9" t="str" s="5">
+        <f>=SUM(B5:B8)</f>
+        <v>formula</v>
+      </c>
+      <c r="C9" t="str" s="5">
+        <f>=SUM(C5:C8)</f>
+        <v>formula</v>
+      </c>
+      <c r="D9" t="str" s="5">
+        <f>=SUM(D5:D8)</f>
+        <v>formula</v>
+      </c>
+      <c r="E9" t="str" s="5">
+        <f>=SUM(E5:E8)</f>
+        <v>formula</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9" t="str" s="5">
+        <f>=SUM(G5:G8)</f>
         <v>formula</v>
       </c>
       <c r="H9" t="str">
@@ -425,50 +430,48 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="5">
+      <c r="A10" t="s" s="6">
         <v>19</v>
       </c>
-      <c r="B10" t="str" s="5">
-        <f>=SUM(B5:B9)</f>
-        <v>formula</v>
-      </c>
-      <c r="C10" t="str" s="5">
-        <f>=SUM(C5:C9)</f>
-        <v>formula</v>
-      </c>
-      <c r="D10" t="str" s="5">
-        <f>=SUM(D5:D9)</f>
-        <v>formula</v>
-      </c>
-      <c r="E10" t="str" s="5">
-        <f>=SUM(E5:E9)</f>
-        <v>formula</v>
-      </c>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
       <c r="F10"/>
-      <c r="G10" t="str" s="5">
-        <f>=SUM(G5:G9)</f>
-        <v>formula</v>
-      </c>
+      <c r="G10"/>
+      <c r="H10"/>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="6">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
+      <c r="B11" s="4">
+        <v>0.42</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="E11" t="str">
+        <f>=C11 - D11</f>
+        <v>formula</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <f>=E11 * F11</f>
+        <v>formula</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -489,77 +492,74 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.00</v>
-      </c>
-      <c r="E13" t="str">
-        <f>=C13 - D13</f>
-        <v>formula</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="str">
-        <f>=E13 * F13</f>
+      <c r="A13" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="B13" t="str" s="5">
+        <f>=SUM(B11:B12)</f>
+        <v>formula</v>
+      </c>
+      <c r="C13" t="str" s="5">
+        <f>=SUM(C11:C12)</f>
+        <v>formula</v>
+      </c>
+      <c r="D13" t="str" s="5">
+        <f>=SUM(D11:D12)</f>
+        <v>formula</v>
+      </c>
+      <c r="E13" t="str" s="5">
+        <f>=SUM(E11:E12)</f>
+        <v>formula</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13" t="str" s="5">
+        <f>=SUM(G11:G12)</f>
         <v>formula</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="5">
-        <v>19</v>
-      </c>
-      <c r="B14" t="str" s="5">
-        <f>=SUM(B12:B13)</f>
-        <v>formula</v>
-      </c>
-      <c r="C14" t="str" s="5">
-        <f>=SUM(C12:C13)</f>
-        <v>formula</v>
-      </c>
-      <c r="D14" t="str" s="5">
-        <f>=SUM(D12:D13)</f>
-        <v>formula</v>
-      </c>
-      <c r="E14" t="str" s="5">
-        <f>=SUM(E12:E13)</f>
-        <v>formula</v>
-      </c>
+      <c r="A14" t="s" s="6">
+        <v>21</v>
+      </c>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
       <c r="F14"/>
-      <c r="G14" t="str" s="5">
-        <f>=SUM(G12:G13)</f>
-        <v>formula</v>
-      </c>
+      <c r="G14"/>
+      <c r="H14"/>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="6">
+      <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15">
-        <v>350</v>
+      <c r="B15" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="E15" t="str">
+        <f>=C15 - D15</f>
+        <v>formula</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="str">
+        <f>=E15 * F15</f>
+        <v>formula</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4">
-        <v>0.62</v>
+        <v>0.05</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -581,10 +581,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -606,10 +606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" s="4">
-        <v>0.07</v>
+        <v>4.13</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -630,164 +630,191 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="5">
-        <v>19</v>
-      </c>
-      <c r="B19" t="str" s="5">
-        <f>=SUM(B16:B18)</f>
-        <v>formula</v>
-      </c>
-      <c r="C19" t="str" s="5">
-        <f>=SUM(C16:C18)</f>
-        <v>formula</v>
-      </c>
-      <c r="D19" t="str" s="5">
-        <f>=SUM(D16:D18)</f>
-        <v>formula</v>
-      </c>
-      <c r="E19" t="str" s="5">
-        <f>=SUM(E16:E18)</f>
-        <v>formula</v>
-      </c>
-      <c r="F19"/>
-      <c r="G19" t="str" s="5">
-        <f>=SUM(G16:G18)</f>
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="4">
+        <v>4.13</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="E19" t="str">
+        <f>=C19 - D19</f>
+        <v>formula</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <f>=E19 * F19</f>
         <v>formula</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20"/>
+      <c r="A20" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="B20" t="str" s="5">
+        <f>=SUM(B15:B19)</f>
+        <v>formula</v>
+      </c>
+      <c r="C20" t="str" s="5">
+        <f>=SUM(C15:C19)</f>
+        <v>formula</v>
+      </c>
+      <c r="D20" t="str" s="5">
+        <f>=SUM(D15:D19)</f>
+        <v>formula</v>
+      </c>
+      <c r="E20" t="str" s="5">
+        <f>=SUM(E15:E19)</f>
+        <v>formula</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20" t="str" s="5">
+        <f>=SUM(G15:G19)</f>
+        <v>formula</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" t="str">
-        <f>=B4 + B11 + B15</f>
-        <v>formula</v>
-      </c>
-      <c r="C21" t="str">
-        <f>=C4 + C11 + C15</f>
-        <v>formula</v>
-      </c>
-      <c r="D21" t="str">
-        <f>=D4 + D11 + D15</f>
-        <v>formula</v>
-      </c>
-      <c r="E21" t="str">
-        <f>=E4 + E11 + E15</f>
-        <v>formula</v>
-      </c>
-      <c r="F21" t="str">
-        <f>=F4 + F11 + F15</f>
-        <v>formula</v>
-      </c>
-      <c r="G21" t="str">
-        <f>=G4 + G11 + G15</f>
-        <v>formula</v>
-      </c>
+      <c r="A21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="str">
-        <f>=B10 + B14 + B19</f>
+        <f>=B4 + B10 + B14</f>
         <v>formula</v>
       </c>
       <c r="C22" t="str">
-        <f>=C10 + C14 + C19</f>
+        <f>=C4 + C10 + C14</f>
         <v>formula</v>
       </c>
       <c r="D22" t="str">
-        <f>=D10 + D14 + D19</f>
+        <f>=D4 + D10 + D14</f>
         <v>formula</v>
       </c>
       <c r="E22" t="str">
-        <f>=E10 + E14 + E19</f>
+        <f>=E4 + E10 + E14</f>
         <v>formula</v>
       </c>
       <c r="F22" t="str">
-        <f>=F10 + F14 + F19</f>
+        <f>=F4 + F10 + F14</f>
         <v>formula</v>
       </c>
       <c r="G22" t="str">
-        <f>=G10 + G14 + G19</f>
-        <v>formula</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="s">
+        <f>=G4 + G10 + G14</f>
+        <v>formula</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" t="s">
-        <v>27</v>
-      </c>
-    </row>
+      <c r="B23" t="str">
+        <f>=B9 + B13 + B20</f>
+        <v>formula</v>
+      </c>
+      <c r="C23" t="str">
+        <f>=C9 + C13 + C20</f>
+        <v>formula</v>
+      </c>
+      <c r="D23" t="str">
+        <f>=D9 + D13 + D20</f>
+        <v>formula</v>
+      </c>
+      <c r="E23" t="str">
+        <f>=E9 + E13 + E20</f>
+        <v>formula</v>
+      </c>
+      <c r="F23" t="str">
+        <f>=F9 + F13 + F20</f>
+        <v>formula</v>
+      </c>
+      <c r="G23" t="str">
+        <f>=G9 + G13 + G20</f>
+        <v>formula</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" t="s">
         <v>28</v>
       </c>
-      <c r="B25" t="str">
-        <f>=(B5+B6+B7+B8+B9+B12+B13+B16+B17+B18)</f>
-        <v>formula</v>
-      </c>
-      <c r="C25" t="str">
-        <f>=(C5+C6+C7+C8+C9+C12+C13+C16+C17+C18)</f>
-        <v>formula</v>
-      </c>
-      <c r="D25" t="str">
-        <f>=(D5+D6+D7+D8+D9+D12+D13+D16+D17+D18)</f>
-        <v>formula</v>
-      </c>
-      <c r="E25" t="str">
-        <f>=(E5+E6+E7+E8+E9+E12+E13+E16+E17+E18)</f>
-        <v>formula</v>
-      </c>
-      <c r="F25"/>
-      <c r="G25" t="str">
-        <f>=(G5+G6+G7+G8+G9+G12+G13+G16+G17+G18)</f>
-        <v>formula</v>
-      </c>
-      <c r="H25" t="str">
-        <f>=135/5*5+50/3*3</f>
-        <v>formula</v>
+      <c r="I25" t="s">
+        <v>29</v>
+      </c>
+      <c r="J25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
+        <v>31</v>
+      </c>
+      <c r="B26" t="str">
+        <f>=(B5+B6+B7+B8+B11+B12+B15+B16+B17+B18+B19)</f>
+        <v>formula</v>
+      </c>
+      <c r="C26" t="str">
+        <f>=(C5+C6+C7+C8+C11+C12+C15+C16+C17+C18+C19)</f>
+        <v>formula</v>
+      </c>
+      <c r="D26" t="str">
+        <f>=(D5+D6+D7+D8+D11+D12+D15+D16+D17+D18+D19)</f>
+        <v>formula</v>
+      </c>
+      <c r="E26" t="str">
+        <f>=(E5+E6+E7+E8+E11+E12+E15+E16+E17+E18+E19)</f>
+        <v>formula</v>
+      </c>
       <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
+      <c r="G26" t="str">
+        <f>=(G5+G6+G7+G8+G11+G12+G15+G16+G17+G18+G19)</f>
+        <v>formula</v>
+      </c>
+      <c r="H26" t="str">
+        <f>=720/4*4+720/5*5</f>
+        <v>formula</v>
+      </c>
+      <c r="I26" t="str">
+        <f>=0/4*4+0/5*5</f>
+        <v>formula</v>
+      </c>
+      <c r="J26" t="str">
+        <f>=0/4*4+0/5*5</f>
+        <v>formula</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
@@ -796,10 +823,12 @@
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
@@ -808,10 +837,12 @@
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
@@ -820,33 +851,51 @@
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
       <c r="F30"/>
-      <c r="G30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>36</v>
-      </c>
-    </row>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
